--- a/output/yearly_benthic_cover_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_58_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.60196721811517</v>
+        <v>45.53712090291253</v>
       </c>
       <c r="M2" t="n">
-        <v>98.6763606889734</v>
+        <v>100.628582268964</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.81321386923952</v>
+        <v>88.010515705362</v>
       </c>
       <c r="C3" t="n">
-        <v>45.79386954682541</v>
+        <v>45.93023962074535</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228282659702246</v>
+        <v>2.228686349041513</v>
       </c>
       <c r="E3" t="n">
-        <v>5.617794430053968</v>
+        <v>5.7062781720491</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7427608865674155</v>
+        <v>0.7428954496805042</v>
       </c>
       <c r="G3" t="n">
-        <v>33.92853095361712</v>
+        <v>33.97384755046254</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16700078210111</v>
+        <v>34.17319068530319</v>
       </c>
       <c r="I3" t="n">
-        <v>6.486588616151307</v>
+        <v>6.542520938321988</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642255541046346</v>
+        <v>4.643096560503151</v>
       </c>
       <c r="K3" t="n">
-        <v>12.18678613076048</v>
+        <v>11.989484294638</v>
       </c>
       <c r="L3" t="n">
-        <v>48.78646224749753</v>
+        <v>48.84542846898385</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7671179250834</v>
+        <v>106.7651523843672</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.6924743007597</v>
+        <v>87.02471915754542</v>
       </c>
       <c r="C4" t="n">
-        <v>42.2975444470375</v>
+        <v>42.5745944370729</v>
       </c>
       <c r="D4" t="n">
-        <v>2.173018174151825</v>
+        <v>2.180816533317455</v>
       </c>
       <c r="E4" t="n">
-        <v>6.381256835927346</v>
+        <v>6.494298447014584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443078678755186</v>
+        <v>0.7444501102672094</v>
       </c>
       <c r="G4" t="n">
-        <v>33.08705655607199</v>
+        <v>33.24412538817742</v>
       </c>
       <c r="H4" t="n">
-        <v>34.23816192227385</v>
+        <v>34.24470507229163</v>
       </c>
       <c r="I4" t="n">
-        <v>5.41674877023718</v>
+        <v>5.463510417307052</v>
       </c>
       <c r="J4" t="n">
-        <v>4.651924174221991</v>
+        <v>4.652813189170059</v>
       </c>
       <c r="K4" t="n">
-        <v>13.3075256992403</v>
+        <v>12.97528084245459</v>
       </c>
       <c r="L4" t="n">
-        <v>44.21474683660687</v>
+        <v>44.26838802774133</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81981698288467</v>
+        <v>99.81826330726882</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.26561265660374</v>
+        <v>85.77421725030415</v>
       </c>
       <c r="C5" t="n">
-        <v>41.71110400795921</v>
+        <v>42.17200946282806</v>
       </c>
       <c r="D5" t="n">
-        <v>2.102268388208177</v>
+        <v>2.119510269401497</v>
       </c>
       <c r="E5" t="n">
-        <v>6.927150105804225</v>
+        <v>7.071899148667284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456236438339748</v>
+        <v>0.7457696340040977</v>
       </c>
       <c r="G5" t="n">
-        <v>32.00979811585614</v>
+        <v>32.30957949971496</v>
       </c>
       <c r="H5" t="n">
-        <v>34.29868761636284</v>
+        <v>34.30540316418849</v>
       </c>
       <c r="I5" t="n">
-        <v>4.521937012576053</v>
+        <v>4.560995321802207</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660147773962342</v>
+        <v>4.661060212525611</v>
       </c>
       <c r="K5" t="n">
-        <v>14.73438734339626</v>
+        <v>14.22578274969583</v>
       </c>
       <c r="L5" t="n">
-        <v>43.40404340502683</v>
+        <v>43.45044360921757</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8495347563823</v>
+        <v>99.84823582174147</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.6342427368626</v>
+        <v>84.28624975806055</v>
       </c>
       <c r="C6" t="n">
-        <v>40.78151714126361</v>
+        <v>41.39226263201676</v>
       </c>
       <c r="D6" t="n">
-        <v>2.021736516083745</v>
+        <v>2.046594130351855</v>
       </c>
       <c r="E6" t="n">
-        <v>7.290782336821287</v>
+        <v>7.463034387020246</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7467451723036213</v>
+        <v>0.7468923202166493</v>
       </c>
       <c r="G6" t="n">
-        <v>30.78359456208814</v>
+        <v>31.19805396221336</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35027792596658</v>
+        <v>34.35704672996587</v>
       </c>
       <c r="I6" t="n">
-        <v>3.773948896701599</v>
+        <v>3.806551226938505</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667157326897633</v>
+        <v>4.668077001354059</v>
       </c>
       <c r="K6" t="n">
-        <v>16.3657572631374</v>
+        <v>15.71375024193945</v>
       </c>
       <c r="L6" t="n">
-        <v>42.72711623413856</v>
+        <v>42.76729281154928</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87439063853958</v>
+        <v>99.87330568550549</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.70496824968092</v>
+        <v>82.59348884554183</v>
       </c>
       <c r="C7" t="n">
-        <v>39.43774366910142</v>
+        <v>40.29050155769151</v>
       </c>
       <c r="D7" t="n">
-        <v>1.926930499525579</v>
+        <v>1.964004285734511</v>
       </c>
       <c r="E7" t="n">
-        <v>7.473726020395311</v>
+        <v>7.691230689876789</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477045178273742</v>
+        <v>0.7478497296611865</v>
       </c>
       <c r="G7" t="n">
-        <v>29.34004840631781</v>
+        <v>29.9390635298213</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39440782005922</v>
+        <v>34.40108756441457</v>
       </c>
       <c r="I7" t="n">
-        <v>3.148997749134535</v>
+        <v>3.176192235651045</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673153236421089</v>
+        <v>4.674060810382416</v>
       </c>
       <c r="K7" t="n">
-        <v>18.29503175031909</v>
+        <v>17.40651115445818</v>
       </c>
       <c r="L7" t="n">
-        <v>42.16239266678221</v>
+        <v>42.19724975376868</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89516808620272</v>
+        <v>99.89426246591836</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.43598830290537</v>
+        <v>87.5310299113238</v>
       </c>
       <c r="C8" t="n">
-        <v>41.63822176198294</v>
+        <v>42.63488524048636</v>
       </c>
       <c r="D8" t="n">
-        <v>1.931060115756097</v>
+        <v>1.968226581808546</v>
       </c>
       <c r="E8" t="n">
-        <v>9.234758538398916</v>
+        <v>9.553172556483593</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493069278329305</v>
+        <v>0.7494574873430062</v>
       </c>
       <c r="G8" t="n">
-        <v>29.81233130105439</v>
+        <v>30.45568682042408</v>
       </c>
       <c r="H8" t="n">
-        <v>34.46811868031481</v>
+        <v>34.47504441777828</v>
       </c>
       <c r="I8" t="n">
-        <v>5.557244440592414</v>
+        <v>5.645332751592507</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683168298955816</v>
+        <v>4.68410929589379</v>
       </c>
       <c r="K8" t="n">
-        <v>13.56401169709463</v>
+        <v>12.46897008867619</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61292120271462</v>
+        <v>44.70837059677163</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81515466179219</v>
+        <v>99.81222592593419</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83.95786898427556</v>
+        <v>85.39711807189887</v>
       </c>
       <c r="C9" t="n">
-        <v>40.02117707005034</v>
+        <v>41.37670559991103</v>
       </c>
       <c r="D9" t="n">
-        <v>1.817622817072347</v>
+        <v>1.871608306441037</v>
       </c>
       <c r="E9" t="n">
-        <v>9.465537422372302</v>
+        <v>9.869733303256327</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7506871677543528</v>
+        <v>0.7508362485682181</v>
       </c>
       <c r="G9" t="n">
-        <v>28.06104955551822</v>
+        <v>28.96064759937135</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53160971670024</v>
+        <v>34.53846743413802</v>
       </c>
       <c r="I9" t="n">
-        <v>4.639567506393386</v>
+        <v>4.713098626572561</v>
       </c>
       <c r="J9" t="n">
-        <v>4.691794798464706</v>
+        <v>4.692726553551364</v>
       </c>
       <c r="K9" t="n">
-        <v>16.04213101572445</v>
+        <v>14.60288192810112</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78232401309764</v>
+        <v>43.86359767333249</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84563209887243</v>
+        <v>99.84318520134464</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>81.25332063616069</v>
+        <v>83.11976273293264</v>
       </c>
       <c r="C10" t="n">
-        <v>38.03473299049033</v>
+        <v>39.8300671501391</v>
       </c>
       <c r="D10" t="n">
-        <v>1.695367202773054</v>
+        <v>1.76967554910705</v>
       </c>
       <c r="E10" t="n">
-        <v>9.474281444320033</v>
+        <v>9.987831118063053</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7518797332984832</v>
+        <v>0.7520207335175916</v>
       </c>
       <c r="G10" t="n">
-        <v>26.17362779833621</v>
+        <v>27.38337384298624</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58646773173024</v>
+        <v>34.5929537418092</v>
       </c>
       <c r="I10" t="n">
-        <v>3.872448392587145</v>
+        <v>3.933778162964546</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699248333115521</v>
+        <v>4.700129584484949</v>
       </c>
       <c r="K10" t="n">
-        <v>18.74667936383931</v>
+        <v>16.88023726706736</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08971077049276</v>
+        <v>43.15877617649986</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87112312482242</v>
+        <v>99.86908059370631</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>78.5308969684307</v>
+        <v>80.7709738372788</v>
       </c>
       <c r="C11" t="n">
-        <v>35.9105725655238</v>
+        <v>38.0904704262096</v>
       </c>
       <c r="D11" t="n">
-        <v>1.573926339455154</v>
+        <v>1.665733321434648</v>
       </c>
       <c r="E11" t="n">
-        <v>9.334206878739673</v>
+        <v>9.948292194731398</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529110362082928</v>
+        <v>0.7530394886179846</v>
       </c>
       <c r="G11" t="n">
-        <v>24.29878443060309</v>
+        <v>25.77500620753896</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63390766558148</v>
+        <v>34.63981647642728</v>
       </c>
       <c r="I11" t="n">
-        <v>3.231466641541193</v>
+        <v>3.282589344666123</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705693976301831</v>
+        <v>4.706496803862406</v>
       </c>
       <c r="K11" t="n">
-        <v>21.46910303156928</v>
+        <v>19.22902616272122</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51275639200171</v>
+        <v>42.57123179543127</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8924319890948</v>
+        <v>99.89072838436208</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>75.73517327036173</v>
+        <v>78.32792420043394</v>
       </c>
       <c r="C12" t="n">
-        <v>33.61291979826238</v>
+        <v>36.15493676223733</v>
       </c>
       <c r="D12" t="n">
-        <v>1.450662782143268</v>
+        <v>1.558706585299506</v>
       </c>
       <c r="E12" t="n">
-        <v>9.052536863684681</v>
+        <v>9.765540838038444</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538044615285712</v>
+        <v>0.7539171380036476</v>
       </c>
       <c r="G12" t="n">
-        <v>22.3958017228433</v>
+        <v>24.11890990883491</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67500523031428</v>
+        <v>34.68018834816777</v>
       </c>
       <c r="I12" t="n">
-        <v>2.696084325294055</v>
+        <v>2.738679269566846</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711277884553571</v>
+        <v>4.711982112522798</v>
       </c>
       <c r="K12" t="n">
-        <v>24.26482672963828</v>
+        <v>21.67207579956607</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0324905098343</v>
+        <v>42.0818044008448</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91023703773496</v>
+        <v>99.90881696264819</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>73.08473869992446</v>
+        <v>75.84000209445516</v>
       </c>
       <c r="C13" t="n">
-        <v>31.3768274160534</v>
+        <v>34.08952448497091</v>
       </c>
       <c r="D13" t="n">
-        <v>1.335161538699865</v>
+        <v>1.450748863663714</v>
       </c>
       <c r="E13" t="n">
-        <v>8.706617430686034</v>
+        <v>9.469922858402658</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545776907053064</v>
+        <v>0.7546741448523887</v>
       </c>
       <c r="G13" t="n">
-        <v>20.61265612984852</v>
+        <v>22.44840784856651</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71057377244411</v>
+        <v>34.71501066320987</v>
       </c>
       <c r="I13" t="n">
-        <v>2.249041570632453</v>
+        <v>2.284524310432601</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716110566908166</v>
+        <v>4.716713405327431</v>
       </c>
       <c r="K13" t="n">
-        <v>26.91526130007554</v>
+        <v>24.15999790554484</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63302005261291</v>
+        <v>41.67440318532961</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92510876874185</v>
+        <v>99.92392557584536</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>81.1254880518193</v>
+        <v>82.93345498900611</v>
       </c>
       <c r="C14" t="n">
-        <v>36.59292692991529</v>
+        <v>38.54712817655327</v>
       </c>
       <c r="D14" t="n">
-        <v>1.336614839455515</v>
+        <v>1.452434385310192</v>
       </c>
       <c r="E14" t="n">
-        <v>11.53163211247637</v>
+        <v>11.93606828629932</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553990357608018</v>
+        <v>0.7555509469227167</v>
       </c>
       <c r="G14" t="n">
-        <v>23.00911172435439</v>
+        <v>24.44785971731255</v>
       </c>
       <c r="H14" t="n">
-        <v>37.12237471189081</v>
+        <v>36.7287142229899</v>
       </c>
       <c r="I14" t="n">
-        <v>2.649111654376406</v>
+        <v>2.890634011904453</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721243973505013</v>
+        <v>4.722193418266981</v>
       </c>
       <c r="K14" t="n">
-        <v>18.87451194818071</v>
+        <v>17.06654501099387</v>
       </c>
       <c r="L14" t="n">
-        <v>44.44435341269121</v>
+        <v>44.29008416286054</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9117922907872</v>
+        <v>99.90375735040769</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>80.12503805380658</v>
+        <v>82.1046439421269</v>
       </c>
       <c r="C15" t="n">
-        <v>35.97889369337832</v>
+        <v>38.16081259637141</v>
       </c>
       <c r="D15" t="n">
-        <v>1.29962418317622</v>
+        <v>1.421575074320291</v>
       </c>
       <c r="E15" t="n">
-        <v>11.58421525791419</v>
+        <v>12.08810755156885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560999320134418</v>
+        <v>0.7562905719051604</v>
       </c>
       <c r="G15" t="n">
-        <v>22.37233730141427</v>
+        <v>23.93219583425042</v>
       </c>
       <c r="H15" t="n">
-        <v>37.15681867076938</v>
+        <v>36.76843907286946</v>
       </c>
       <c r="I15" t="n">
-        <v>2.230318133435059</v>
+        <v>2.411219762805467</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725624575084013</v>
+        <v>4.726816074407253</v>
       </c>
       <c r="K15" t="n">
-        <v>19.87496194619343</v>
+        <v>17.89535605787312</v>
       </c>
       <c r="L15" t="n">
-        <v>44.07186933865302</v>
+        <v>43.86353595653589</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92572497822476</v>
+        <v>99.91970461078041</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>77.33357590145938</v>
+        <v>79.54668066375773</v>
       </c>
       <c r="C16" t="n">
-        <v>33.53058092959245</v>
+        <v>35.97509738739855</v>
       </c>
       <c r="D16" t="n">
-        <v>1.197683920239293</v>
+        <v>1.32557169743798</v>
       </c>
       <c r="E16" t="n">
-        <v>10.98558430539367</v>
+        <v>11.60693398119538</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567061425514122</v>
+        <v>0.756927905407293</v>
       </c>
       <c r="G16" t="n">
-        <v>20.6174900336095</v>
+        <v>22.31598037169712</v>
       </c>
       <c r="H16" t="n">
-        <v>37.18660951465386</v>
+        <v>36.79942419804857</v>
       </c>
       <c r="I16" t="n">
-        <v>1.860088594065308</v>
+        <v>2.011043101175805</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729413390946328</v>
+        <v>4.730799408795582</v>
       </c>
       <c r="K16" t="n">
-        <v>22.66642409854064</v>
+        <v>20.45331933624227</v>
       </c>
       <c r="L16" t="n">
-        <v>43.74104169038261</v>
+        <v>43.5046049496146</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93804671851569</v>
+        <v>99.93302167325541</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>79.34359633365725</v>
+        <v>81.35745539937872</v>
       </c>
       <c r="C17" t="n">
-        <v>34.99640092412346</v>
+        <v>37.29257323723966</v>
       </c>
       <c r="D17" t="n">
-        <v>1.198591203862739</v>
+        <v>1.326653691819004</v>
       </c>
       <c r="E17" t="n">
-        <v>11.86418275377369</v>
+        <v>12.42653258896702</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572793714971268</v>
+        <v>0.7575457458017988</v>
       </c>
       <c r="G17" t="n">
-        <v>21.2028584806263</v>
+        <v>22.81228117461199</v>
       </c>
       <c r="H17" t="n">
-        <v>37.78452959612616</v>
+        <v>37.30754707355919</v>
       </c>
       <c r="I17" t="n">
-        <v>1.803158855914183</v>
+        <v>1.992234213358476</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732996071857044</v>
+        <v>4.734660911261244</v>
       </c>
       <c r="K17" t="n">
-        <v>20.65640366634276</v>
+        <v>18.64254460062128</v>
       </c>
       <c r="L17" t="n">
-        <v>44.2871356115419</v>
+        <v>43.99852851601472</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93994020200812</v>
+        <v>99.93364635387564</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>76.82031820167914</v>
+        <v>78.90023907041939</v>
       </c>
       <c r="C18" t="n">
-        <v>32.75007240776983</v>
+        <v>35.14249606854025</v>
       </c>
       <c r="D18" t="n">
-        <v>1.111052872619113</v>
+        <v>1.238370530706393</v>
       </c>
       <c r="E18" t="n">
-        <v>11.24829198621588</v>
+        <v>11.87649310009464</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577734486489556</v>
+        <v>0.7580774537526432</v>
       </c>
       <c r="G18" t="n">
-        <v>19.65432146232749</v>
+        <v>21.29422087997466</v>
       </c>
       <c r="H18" t="n">
-        <v>37.80918162478124</v>
+        <v>37.33373258052752</v>
       </c>
       <c r="I18" t="n">
-        <v>1.503612753030493</v>
+        <v>1.661360439409506</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736084054055974</v>
+        <v>4.737984085954023</v>
       </c>
       <c r="K18" t="n">
-        <v>23.17968179832087</v>
+        <v>21.09976092958062</v>
       </c>
       <c r="L18" t="n">
-        <v>44.02015804791169</v>
+        <v>43.70240316261916</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94991225400238</v>
+        <v>99.94466016074004</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>75.90518207916546</v>
+        <v>77.94914152949914</v>
       </c>
       <c r="C19" t="n">
-        <v>32.03664052498492</v>
+        <v>34.44033321214137</v>
       </c>
       <c r="D19" t="n">
-        <v>1.078750621164525</v>
+        <v>1.204586614625043</v>
       </c>
       <c r="E19" t="n">
-        <v>11.134815891128</v>
+        <v>11.78441807384474</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581998327073841</v>
+        <v>0.7585285647098426</v>
       </c>
       <c r="G19" t="n">
-        <v>19.08290056086417</v>
+        <v>20.71329445013106</v>
       </c>
       <c r="H19" t="n">
-        <v>37.83045609980511</v>
+        <v>37.35594885375508</v>
       </c>
       <c r="I19" t="n">
-        <v>1.281310119075122</v>
+        <v>1.391561442996863</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738748954421153</v>
+        <v>4.740803529436518</v>
       </c>
       <c r="K19" t="n">
-        <v>24.09481792083453</v>
+        <v>22.05085847050085</v>
       </c>
       <c r="L19" t="n">
-        <v>43.82585523562109</v>
+        <v>43.46245052216824</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95731368144054</v>
+        <v>99.95364220481045</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.30497419708257</v>
+        <v>75.31913760459237</v>
       </c>
       <c r="C20" t="n">
-        <v>29.63241876254163</v>
+        <v>32.02409620104237</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9896051478478869</v>
+        <v>1.111155344644102</v>
       </c>
       <c r="E20" t="n">
-        <v>10.39270646983126</v>
+        <v>11.06375571594348</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585681421976912</v>
+        <v>0.7589180485369008</v>
       </c>
       <c r="G20" t="n">
-        <v>17.50593349416979</v>
+        <v>19.10671059599506</v>
       </c>
       <c r="H20" t="n">
-        <v>37.84883293847368</v>
+        <v>37.37513011943163</v>
       </c>
       <c r="I20" t="n">
-        <v>1.068277115826701</v>
+        <v>1.160229976685576</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741050888735572</v>
+        <v>4.743237803355632</v>
       </c>
       <c r="K20" t="n">
-        <v>26.69502580291742</v>
+        <v>24.68086239540762</v>
       </c>
       <c r="L20" t="n">
-        <v>43.63696348678886</v>
+        <v>43.25638691902232</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96440805224792</v>
+        <v>99.96134551547232</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.06932387159056</v>
+        <v>81.48349216964994</v>
       </c>
       <c r="C21" t="n">
-        <v>34.03458573816801</v>
+        <v>35.90785097226186</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9901479421633409</v>
+        <v>1.111884837943383</v>
       </c>
       <c r="E21" t="n">
-        <v>12.70329063512473</v>
+        <v>13.13968279616602</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7589842136746483</v>
+        <v>0.7594162917697482</v>
       </c>
       <c r="G21" t="n">
-        <v>19.60083077619515</v>
+        <v>20.92044119090004</v>
       </c>
       <c r="H21" t="n">
-        <v>39.95488821639492</v>
+        <v>39.20085425753922</v>
       </c>
       <c r="I21" t="n">
-        <v>1.317530752571222</v>
+        <v>1.604860971770588</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743651335466554</v>
+        <v>4.746351823560929</v>
       </c>
       <c r="K21" t="n">
-        <v>19.93067612840943</v>
+        <v>18.51650783035007</v>
       </c>
       <c r="L21" t="n">
-        <v>45.9908445171365</v>
+        <v>45.52218092928177</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95610638371394</v>
+        <v>99.94653973189369</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_58_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.53712090291253</v>
+        <v>45.40275779663904</v>
       </c>
       <c r="M2" t="n">
-        <v>100.628582268964</v>
+        <v>100.3258537104332</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.010515705362</v>
+        <v>88.08304722575176</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93023962074535</v>
+        <v>45.93907071405275</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228686349041513</v>
+        <v>2.228865642161935</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7062781720491</v>
+        <v>5.7153853678044</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428954496805042</v>
+        <v>0.7429552140539782</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97384755046254</v>
+        <v>33.97613392072956</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17319068530319</v>
+        <v>34.17593984648299</v>
       </c>
       <c r="I3" t="n">
-        <v>6.542520938321988</v>
+        <v>6.600297146681525</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643096560503151</v>
+        <v>4.643470087837364</v>
       </c>
       <c r="K3" t="n">
-        <v>11.989484294638</v>
+        <v>11.91695277424824</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84542846898385</v>
+        <v>48.90707404357968</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7651523843672</v>
+        <v>106.7630975318807</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02471915754542</v>
+        <v>87.30411408321878</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5745944370729</v>
+        <v>42.80111493925599</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180816533317455</v>
+        <v>2.192053920225521</v>
       </c>
       <c r="E4" t="n">
-        <v>6.494298447014584</v>
+        <v>6.539627740903143</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444501102672094</v>
+        <v>0.744518728522633</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24412538817742</v>
+        <v>33.41498749238267</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24470507229163</v>
+        <v>34.24786151204111</v>
       </c>
       <c r="I4" t="n">
-        <v>5.463510417307052</v>
+        <v>5.511822635877247</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652813189170059</v>
+        <v>4.653242053266456</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97528084245459</v>
+        <v>12.69588591678122</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26838802774133</v>
+        <v>44.31965755655496</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81826330726882</v>
+        <v>99.81665841259216</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.77421725030415</v>
+        <v>86.27864218567582</v>
       </c>
       <c r="C5" t="n">
-        <v>42.17200946282806</v>
+        <v>42.63124690614064</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119510269401497</v>
+        <v>2.142521010264714</v>
       </c>
       <c r="E5" t="n">
-        <v>7.071899148667284</v>
+        <v>7.15874636797297</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457696340040977</v>
+        <v>0.7458422665460651</v>
       </c>
       <c r="G5" t="n">
-        <v>32.30957949971496</v>
+        <v>32.6599232343687</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30540316418849</v>
+        <v>34.30874426111899</v>
       </c>
       <c r="I5" t="n">
-        <v>4.560995321802207</v>
+        <v>4.601350879491478</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661060212525611</v>
+        <v>4.661514165912907</v>
       </c>
       <c r="K5" t="n">
-        <v>14.22578274969583</v>
+        <v>13.72135781432416</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45044360921757</v>
+        <v>43.49428909520527</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84823582174147</v>
+        <v>99.84689381567009</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.28624975806055</v>
+        <v>85.08434450820756</v>
       </c>
       <c r="C6" t="n">
-        <v>41.39226263201676</v>
+        <v>42.15181171272464</v>
       </c>
       <c r="D6" t="n">
-        <v>2.046594130351855</v>
+        <v>2.084672299518342</v>
       </c>
       <c r="E6" t="n">
-        <v>7.463034387020246</v>
+        <v>7.605496054172979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468923202166493</v>
+        <v>0.7469643704689669</v>
       </c>
       <c r="G6" t="n">
-        <v>31.19805396221336</v>
+        <v>31.77809549819622</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35704672996587</v>
+        <v>34.36036104157247</v>
       </c>
       <c r="I6" t="n">
-        <v>3.806551226938505</v>
+        <v>3.840227928847538</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668077001354059</v>
+        <v>4.668527315431043</v>
       </c>
       <c r="K6" t="n">
-        <v>15.71375024193945</v>
+        <v>14.91565549179245</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76729281154928</v>
+        <v>42.80471749327479</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87330568550549</v>
+        <v>99.87218469779188</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.59348884554183</v>
+        <v>83.65160568384141</v>
       </c>
       <c r="C7" t="n">
-        <v>40.29050155769151</v>
+        <v>41.31585438810809</v>
       </c>
       <c r="D7" t="n">
-        <v>1.964004285734511</v>
+        <v>2.015216168348422</v>
       </c>
       <c r="E7" t="n">
-        <v>7.691230689876789</v>
+        <v>7.886145722402812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478497296611865</v>
+        <v>0.7479181198616959</v>
       </c>
       <c r="G7" t="n">
-        <v>29.9390635298213</v>
+        <v>30.71932785890685</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40108756441457</v>
+        <v>34.40423351363801</v>
       </c>
       <c r="I7" t="n">
-        <v>3.176192235651045</v>
+        <v>3.204276051548021</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674060810382416</v>
+        <v>4.674488249135599</v>
       </c>
       <c r="K7" t="n">
-        <v>17.40651115445818</v>
+        <v>16.34839431615858</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19724975376868</v>
+        <v>42.2290782977098</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89426246591836</v>
+        <v>99.89332700197647</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.5310299113238</v>
+        <v>88.37427266451097</v>
       </c>
       <c r="C8" t="n">
-        <v>42.63488524048636</v>
+        <v>43.5353616081154</v>
       </c>
       <c r="D8" t="n">
-        <v>1.968226581808546</v>
+        <v>2.019462216759136</v>
       </c>
       <c r="E8" t="n">
-        <v>9.553172556483593</v>
+        <v>9.660647941112298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494574873430062</v>
+        <v>0.7494939788658372</v>
       </c>
       <c r="G8" t="n">
-        <v>30.45568682042408</v>
+        <v>31.19748621783688</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47504441777828</v>
+        <v>34.47672302782852</v>
       </c>
       <c r="I8" t="n">
-        <v>5.645332751592507</v>
+        <v>5.586121914196807</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68410929589379</v>
+        <v>4.684337367911484</v>
       </c>
       <c r="K8" t="n">
-        <v>12.46897008867619</v>
+        <v>11.62572733548905</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70837059677163</v>
+        <v>44.65309849853678</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81222592593419</v>
+        <v>99.81418744214122</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.39711807189887</v>
+        <v>86.32936480793002</v>
       </c>
       <c r="C9" t="n">
-        <v>41.37670559991103</v>
+        <v>42.3580327638539</v>
       </c>
       <c r="D9" t="n">
-        <v>1.871608306441037</v>
+        <v>1.926613449727454</v>
       </c>
       <c r="E9" t="n">
-        <v>9.869733303256327</v>
+        <v>9.993727862083672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508362485682181</v>
+        <v>0.7508435594552906</v>
       </c>
       <c r="G9" t="n">
-        <v>28.96064759937135</v>
+        <v>29.76312012483681</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53846743413802</v>
+        <v>34.53880373494337</v>
       </c>
       <c r="I9" t="n">
-        <v>4.713098626572561</v>
+        <v>4.66348383028786</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692726553551364</v>
+        <v>4.692772246595567</v>
       </c>
       <c r="K9" t="n">
-        <v>14.60288192810112</v>
+        <v>13.67063519206997</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86359767333249</v>
+        <v>43.81616199090401</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84318520134464</v>
+        <v>99.84482994682787</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.11976273293264</v>
+        <v>84.09206659743984</v>
       </c>
       <c r="C10" t="n">
-        <v>39.8300671501391</v>
+        <v>40.84471287315302</v>
       </c>
       <c r="D10" t="n">
-        <v>1.76967554910705</v>
+        <v>1.826018243550456</v>
       </c>
       <c r="E10" t="n">
-        <v>9.987831118063053</v>
+        <v>10.12062588103543</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520207335175916</v>
+        <v>0.7520019951789632</v>
       </c>
       <c r="G10" t="n">
-        <v>27.38337384298624</v>
+        <v>28.20908384119504</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5929537418092</v>
+        <v>34.59209177823231</v>
       </c>
       <c r="I10" t="n">
-        <v>3.933778162964546</v>
+        <v>3.892232388379131</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700129584484949</v>
+        <v>4.70001246986852</v>
       </c>
       <c r="K10" t="n">
-        <v>16.88023726706736</v>
+        <v>15.90793340256015</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15877617649986</v>
+        <v>43.11781250677882</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86908059370631</v>
+        <v>99.87045878249199</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.7709738372788</v>
+        <v>81.74937724387343</v>
       </c>
       <c r="C11" t="n">
-        <v>38.0904704262096</v>
+        <v>39.10562843911276</v>
       </c>
       <c r="D11" t="n">
-        <v>1.665733321434648</v>
+        <v>1.721765268086709</v>
       </c>
       <c r="E11" t="n">
-        <v>9.948292194731398</v>
+        <v>10.08411207781397</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530394886179846</v>
+        <v>0.7529978718462959</v>
       </c>
       <c r="G11" t="n">
-        <v>25.77500620753896</v>
+        <v>26.59854082721467</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63981647642728</v>
+        <v>34.63790210492961</v>
       </c>
       <c r="I11" t="n">
-        <v>3.282589344666123</v>
+        <v>3.247822394942828</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706496803862406</v>
+        <v>4.70623669903935</v>
       </c>
       <c r="K11" t="n">
-        <v>19.22902616272122</v>
+        <v>18.25062275612659</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57123179543127</v>
+        <v>42.53563123841677</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89072838436208</v>
+        <v>99.89188243365612</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.32792420043394</v>
+        <v>79.30297754065255</v>
       </c>
       <c r="C12" t="n">
-        <v>36.15493676223733</v>
+        <v>37.16210278548284</v>
       </c>
       <c r="D12" t="n">
-        <v>1.558706585299506</v>
+        <v>1.613923149153152</v>
       </c>
       <c r="E12" t="n">
-        <v>9.765540838038444</v>
+        <v>9.904097713539766</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539171380036476</v>
+        <v>0.7538554789567571</v>
       </c>
       <c r="G12" t="n">
-        <v>24.11890990883491</v>
+        <v>24.93255124285334</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68018834816777</v>
+        <v>34.67735203201082</v>
       </c>
       <c r="I12" t="n">
-        <v>2.738679269566846</v>
+        <v>2.709601180658981</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711982112522798</v>
+        <v>4.711596743479732</v>
       </c>
       <c r="K12" t="n">
-        <v>21.67207579956607</v>
+        <v>20.69702245934745</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0818044008448</v>
+        <v>42.05065746642131</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90881696264819</v>
+        <v>99.90978271125159</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.84000209445516</v>
+        <v>76.7334490667759</v>
       </c>
       <c r="C13" t="n">
-        <v>34.08952448497091</v>
+        <v>35.01123260794014</v>
       </c>
       <c r="D13" t="n">
-        <v>1.450748863663714</v>
+        <v>1.501624976192222</v>
       </c>
       <c r="E13" t="n">
-        <v>9.469922858402658</v>
+        <v>9.591665001503326</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546741448523887</v>
+        <v>0.7545956506125512</v>
       </c>
       <c r="G13" t="n">
-        <v>22.44840784856651</v>
+        <v>23.1977226958458</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71501066320987</v>
+        <v>34.71139992817735</v>
       </c>
       <c r="I13" t="n">
-        <v>2.284524310432601</v>
+        <v>2.260217998116217</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716713405327431</v>
+        <v>4.716222816328445</v>
       </c>
       <c r="K13" t="n">
-        <v>24.15999790554484</v>
+        <v>23.26655093322408</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67440318532961</v>
+        <v>41.64694975937304</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92392557584536</v>
+        <v>99.92473330053726</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.93345498900611</v>
+        <v>83.54222692293254</v>
       </c>
       <c r="C14" t="n">
-        <v>38.54712817655327</v>
+        <v>39.21412108112095</v>
       </c>
       <c r="D14" t="n">
-        <v>1.452434385310192</v>
+        <v>1.5034032235984</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93606828629932</v>
+        <v>11.9370781627763</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555509469227167</v>
+        <v>0.7554892543949132</v>
       </c>
       <c r="G14" t="n">
-        <v>24.44785971731255</v>
+        <v>25.06458840602428</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7287142229899</v>
+        <v>36.59190031212496</v>
       </c>
       <c r="I14" t="n">
-        <v>2.890634011904453</v>
+        <v>2.967959724045492</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722193418266981</v>
+        <v>4.721807839968208</v>
       </c>
       <c r="K14" t="n">
-        <v>17.06654501099387</v>
+        <v>16.45777307706746</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29008416286054</v>
+        <v>44.22929086922132</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90375735040769</v>
+        <v>99.90118502740972</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.1046439421269</v>
+        <v>82.67165232871461</v>
       </c>
       <c r="C15" t="n">
-        <v>38.16081259637141</v>
+        <v>38.80220108091564</v>
       </c>
       <c r="D15" t="n">
-        <v>1.421575074320291</v>
+        <v>1.470879070863653</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08810755156885</v>
+        <v>12.09146328314068</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562905719051604</v>
+        <v>0.756243409173613</v>
       </c>
       <c r="G15" t="n">
-        <v>23.93219583425042</v>
+        <v>24.52234897966473</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76843907286946</v>
+        <v>36.62842757749844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.411219762805467</v>
+        <v>2.475768701038425</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726816074407253</v>
+        <v>4.726521307335082</v>
       </c>
       <c r="K15" t="n">
-        <v>17.89535605787312</v>
+        <v>17.32834767128537</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86353595653589</v>
+        <v>43.78700792213108</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91970461078041</v>
+        <v>99.91755667433209</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.54668066375773</v>
+        <v>80.17551952075895</v>
       </c>
       <c r="C16" t="n">
-        <v>35.97509738739855</v>
+        <v>36.6886586989201</v>
       </c>
       <c r="D16" t="n">
-        <v>1.32557169743798</v>
+        <v>1.375655238736497</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60693398119538</v>
+        <v>11.65282113923556</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756927905407293</v>
+        <v>0.7568926413979811</v>
       </c>
       <c r="G16" t="n">
-        <v>22.31598037169712</v>
+        <v>22.93478675999697</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79942419804857</v>
+        <v>36.65987294974602</v>
       </c>
       <c r="I16" t="n">
-        <v>2.011043101175805</v>
+        <v>2.064911782908541</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730799408795582</v>
+        <v>4.730579008737382</v>
       </c>
       <c r="K16" t="n">
-        <v>20.45331933624227</v>
+        <v>19.82448047924106</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5046049496146</v>
+        <v>43.41808946903221</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93302167325541</v>
+        <v>99.93122864719336</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.35745539937872</v>
+        <v>81.80053777325941</v>
       </c>
       <c r="C17" t="n">
-        <v>37.29257323723966</v>
+        <v>37.87283964938661</v>
       </c>
       <c r="D17" t="n">
-        <v>1.326653691819004</v>
+        <v>1.376813297017087</v>
       </c>
       <c r="E17" t="n">
-        <v>12.42653258896702</v>
+        <v>12.41161180980641</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575457458017988</v>
+        <v>0.7575298110653561</v>
       </c>
       <c r="G17" t="n">
-        <v>22.81228117461199</v>
+        <v>23.35876696065694</v>
       </c>
       <c r="H17" t="n">
-        <v>37.30754707355919</v>
+        <v>37.09540724424163</v>
       </c>
       <c r="I17" t="n">
-        <v>1.992234213358476</v>
+        <v>2.0658473313135</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734660911261244</v>
+        <v>4.734561319158476</v>
       </c>
       <c r="K17" t="n">
-        <v>18.64254460062128</v>
+        <v>18.19946222674061</v>
       </c>
       <c r="L17" t="n">
-        <v>43.99852851601472</v>
+        <v>43.85889446666649</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93364635387564</v>
+        <v>99.93119634279371</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.90023907041939</v>
+        <v>79.35706591215951</v>
       </c>
       <c r="C18" t="n">
-        <v>35.14249606854025</v>
+        <v>35.74817325790612</v>
       </c>
       <c r="D18" t="n">
-        <v>1.238370530706393</v>
+        <v>1.28717991384967</v>
       </c>
       <c r="E18" t="n">
-        <v>11.87649310009464</v>
+        <v>11.89072117179701</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580774537526432</v>
+        <v>0.7580779921038455</v>
       </c>
       <c r="G18" t="n">
-        <v>21.29422087997466</v>
+        <v>21.83806309046693</v>
       </c>
       <c r="H18" t="n">
-        <v>37.33373258052752</v>
+        <v>37.122251070807</v>
       </c>
       <c r="I18" t="n">
-        <v>1.661360439409506</v>
+        <v>1.722785222486019</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737984085954023</v>
+        <v>4.737987450649035</v>
       </c>
       <c r="K18" t="n">
-        <v>21.09976092958062</v>
+        <v>20.64293408784049</v>
       </c>
       <c r="L18" t="n">
-        <v>43.70240316261916</v>
+        <v>43.55150800616135</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94466016074004</v>
+        <v>99.94261535190796</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.94914152949914</v>
+        <v>78.39387323952296</v>
       </c>
       <c r="C19" t="n">
-        <v>34.44033321214137</v>
+        <v>35.05012522092619</v>
       </c>
       <c r="D19" t="n">
-        <v>1.204586614625043</v>
+        <v>1.252537747167559</v>
       </c>
       <c r="E19" t="n">
-        <v>11.78441807384474</v>
+        <v>11.81012535934498</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585285647098426</v>
+        <v>0.7585410396609281</v>
       </c>
       <c r="G19" t="n">
-        <v>20.71329445013106</v>
+        <v>21.25033031631895</v>
       </c>
       <c r="H19" t="n">
-        <v>37.35594885375508</v>
+        <v>37.14492600379646</v>
       </c>
       <c r="I19" t="n">
-        <v>1.391561442996863</v>
+        <v>1.436531275353279</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740803529436518</v>
+        <v>4.740881497880801</v>
       </c>
       <c r="K19" t="n">
-        <v>22.05085847050085</v>
+        <v>21.60612676047704</v>
       </c>
       <c r="L19" t="n">
-        <v>43.46245052216824</v>
+        <v>43.29589287352771</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95364220481045</v>
+        <v>99.95214485493095</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.31913760459237</v>
+        <v>75.86018858187984</v>
       </c>
       <c r="C20" t="n">
-        <v>32.02409620104237</v>
+        <v>32.73736803753725</v>
       </c>
       <c r="D20" t="n">
-        <v>1.111155344644102</v>
+        <v>1.160660402760676</v>
       </c>
       <c r="E20" t="n">
-        <v>11.06375571594348</v>
+        <v>11.14344100858015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589180485369008</v>
+        <v>0.7589402541133231</v>
       </c>
       <c r="G20" t="n">
-        <v>19.10671059599506</v>
+        <v>19.69155580301778</v>
       </c>
       <c r="H20" t="n">
-        <v>37.37513011943163</v>
+        <v>37.16447509938724</v>
       </c>
       <c r="I20" t="n">
-        <v>1.160229976685576</v>
+        <v>1.197739425812409</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743237803355632</v>
+        <v>4.74337658820827</v>
       </c>
       <c r="K20" t="n">
-        <v>24.68086239540762</v>
+        <v>24.13981141812016</v>
       </c>
       <c r="L20" t="n">
-        <v>43.25638691902232</v>
+        <v>43.082916897805</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96134551547232</v>
+        <v>99.9600963534624</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.48349216964994</v>
+        <v>81.76663802503175</v>
       </c>
       <c r="C21" t="n">
-        <v>35.90785097226186</v>
+        <v>36.38962597585353</v>
       </c>
       <c r="D21" t="n">
-        <v>1.111884837943383</v>
+        <v>1.16148360981348</v>
       </c>
       <c r="E21" t="n">
-        <v>13.13968279616602</v>
+        <v>13.11513191215322</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594162917697482</v>
+        <v>0.7594785381526138</v>
       </c>
       <c r="G21" t="n">
-        <v>20.92044119090004</v>
+        <v>21.37934152953767</v>
       </c>
       <c r="H21" t="n">
-        <v>39.20085425753922</v>
+        <v>38.86465362432054</v>
       </c>
       <c r="I21" t="n">
-        <v>1.604860971770588</v>
+        <v>1.739807947600404</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746351823560929</v>
+        <v>4.746740863453837</v>
       </c>
       <c r="K21" t="n">
-        <v>18.51650783035007</v>
+        <v>18.23336197496825</v>
       </c>
       <c r="L21" t="n">
-        <v>45.52218092928177</v>
+        <v>45.31905955416449</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94653973189369</v>
+        <v>99.94204750498626</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_58_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.40275779663904</v>
+        <v>43.75294782969407</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3258537104332</v>
+        <v>96.22058386115123</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08304722575176</v>
+        <v>81.46675887499507</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93907071405275</v>
+        <v>43.22231443055063</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228865642161935</v>
+        <v>2.179906046827127</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7153853678044</v>
+        <v>4.145416897226593</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429552140539782</v>
+        <v>0.73762581962119</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97613392072956</v>
+        <v>32.7894201210247</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17593984648299</v>
+        <v>33.93078770257473</v>
       </c>
       <c r="I3" t="n">
-        <v>6.600297146681525</v>
+        <v>3.073440915088292</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643470087837364</v>
+        <v>4.610161372632437</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91695277424824</v>
+        <v>18.53324112500493</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90707404357968</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630975318807</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30411408321878</v>
+        <v>88.55430763730568</v>
       </c>
       <c r="C4" t="n">
-        <v>42.80111493925599</v>
+        <v>42.82975269583261</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192053920225521</v>
+        <v>2.185625399004321</v>
       </c>
       <c r="E4" t="n">
-        <v>6.539627740903143</v>
+        <v>6.533652090745201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744518728522633</v>
+        <v>0.7395611057054439</v>
       </c>
       <c r="G4" t="n">
-        <v>33.41498749238267</v>
+        <v>33.48328519989643</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24786151204111</v>
+        <v>34.01981086245041</v>
       </c>
       <c r="I4" t="n">
-        <v>5.511822635877247</v>
+        <v>6.970116068844853</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653242053266456</v>
+        <v>4.622256910659023</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69588591678122</v>
+        <v>11.44569236269432</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31965755655496</v>
+        <v>45.49282571998063</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81665841259216</v>
+        <v>99.76827077850756</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.27864218567582</v>
+        <v>87.35170608795892</v>
       </c>
       <c r="C5" t="n">
-        <v>42.63124690614064</v>
+        <v>42.70759392223307</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142521010264714</v>
+        <v>2.12806078543488</v>
       </c>
       <c r="E5" t="n">
-        <v>7.15874636797297</v>
+        <v>7.331792088070012</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458422665460651</v>
+        <v>0.74120397820271</v>
       </c>
       <c r="G5" t="n">
-        <v>32.6599232343687</v>
+        <v>32.60140838127716</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30874426111899</v>
+        <v>34.09538299732465</v>
       </c>
       <c r="I5" t="n">
-        <v>4.601350879491478</v>
+        <v>5.821332993882558</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661514165912907</v>
+        <v>4.632524863766936</v>
       </c>
       <c r="K5" t="n">
-        <v>13.72135781432416</v>
+        <v>12.6482939120411</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49428909520527</v>
+        <v>44.45049783048015</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84689381567009</v>
+        <v>99.80638566475432</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.08434450820756</v>
+        <v>85.92325057389357</v>
       </c>
       <c r="C6" t="n">
-        <v>42.15181171272464</v>
+        <v>42.182528190292</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084672299518342</v>
+        <v>2.059665251729285</v>
       </c>
       <c r="E6" t="n">
-        <v>7.605496054172979</v>
+        <v>7.906192397302579</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469643704689669</v>
+        <v>0.7426015208759384</v>
       </c>
       <c r="G6" t="n">
-        <v>31.77809549819622</v>
+        <v>31.55360432368025</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36036104157247</v>
+        <v>34.15966996029316</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840227928847538</v>
+        <v>4.860257614537744</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668527315431043</v>
+        <v>4.641259505474614</v>
       </c>
       <c r="K6" t="n">
-        <v>14.91565549179245</v>
+        <v>14.07674942610644</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80471749327479</v>
+        <v>43.57901868932705</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87218469779188</v>
+        <v>99.83829630572549</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.65160568384141</v>
+        <v>84.22574814273912</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31585438810809</v>
+        <v>41.23959684223051</v>
       </c>
       <c r="D7" t="n">
-        <v>2.015216168348422</v>
+        <v>1.978628451915769</v>
       </c>
       <c r="E7" t="n">
-        <v>7.886145722402812</v>
+        <v>8.271245603233563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479181198616959</v>
+        <v>0.7437937629488242</v>
       </c>
       <c r="G7" t="n">
-        <v>30.71932785890685</v>
+        <v>30.31213893758117</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40423351363801</v>
+        <v>34.2145130956459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204276051548021</v>
+        <v>4.056717272983748</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674488249135599</v>
+        <v>4.648711018430149</v>
       </c>
       <c r="K7" t="n">
-        <v>16.34839431615858</v>
+        <v>15.77425185726088</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2290782977098</v>
+        <v>42.85114414454922</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89332700197647</v>
+        <v>99.86499284404061</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.37427266451097</v>
+        <v>82.32110932402772</v>
       </c>
       <c r="C8" t="n">
-        <v>43.5353616081154</v>
+        <v>39.964600891549</v>
       </c>
       <c r="D8" t="n">
-        <v>2.019462216759136</v>
+        <v>1.888304374586123</v>
       </c>
       <c r="E8" t="n">
-        <v>9.660647941112298</v>
+        <v>8.457869819768533</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494939788658372</v>
+        <v>0.7448133127796676</v>
       </c>
       <c r="G8" t="n">
-        <v>31.19748621783688</v>
+        <v>28.92839456719464</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47672302782852</v>
+        <v>34.2614123878647</v>
       </c>
       <c r="I8" t="n">
-        <v>5.586121914196807</v>
+        <v>3.385231656961132</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684337367911484</v>
+        <v>4.655083204872921</v>
       </c>
       <c r="K8" t="n">
-        <v>11.62572733548905</v>
+        <v>17.67889067597229</v>
       </c>
       <c r="L8" t="n">
-        <v>44.65309849853678</v>
+        <v>42.2438218415625</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81418744214122</v>
+        <v>99.88731340908379</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.32936480793002</v>
+        <v>80.18629381460057</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3580327638539</v>
+        <v>38.35473762836866</v>
       </c>
       <c r="D9" t="n">
-        <v>1.926613449727454</v>
+        <v>1.787759863376023</v>
       </c>
       <c r="E9" t="n">
-        <v>9.993727862083672</v>
+        <v>8.478245805109024</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508435594552906</v>
+        <v>0.7456877784748406</v>
       </c>
       <c r="G9" t="n">
-        <v>29.76312012483681</v>
+        <v>27.38807546875002</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53880373494337</v>
+        <v>34.30163780984265</v>
       </c>
       <c r="I9" t="n">
-        <v>4.66348383028786</v>
+        <v>2.824338473580249</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692772246595567</v>
+        <v>4.660548615467753</v>
       </c>
       <c r="K9" t="n">
-        <v>13.67063519206997</v>
+        <v>19.81370618539942</v>
       </c>
       <c r="L9" t="n">
-        <v>43.81616199090401</v>
+        <v>41.73752197353856</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84482994682787</v>
+        <v>99.90596578730664</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.09206659743984</v>
+        <v>85.35083199612713</v>
       </c>
       <c r="C10" t="n">
-        <v>40.84471287315302</v>
+        <v>41.80053124906617</v>
       </c>
       <c r="D10" t="n">
-        <v>1.826018243550456</v>
+        <v>1.789884719361596</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12062588103543</v>
+        <v>10.44433585796298</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520019951789632</v>
+        <v>0.7465740715234321</v>
       </c>
       <c r="G10" t="n">
-        <v>28.20908384119504</v>
+        <v>28.86941894897444</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59209177823231</v>
+        <v>35.79119845872772</v>
       </c>
       <c r="I10" t="n">
-        <v>3.892232388379131</v>
+        <v>3.043331992555512</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70001246986852</v>
+        <v>4.66608794702145</v>
       </c>
       <c r="K10" t="n">
-        <v>15.90793340256015</v>
+        <v>14.64916800387287</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11781250677882</v>
+        <v>43.44897677670754</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87045878249199</v>
+        <v>99.89867602964657</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.74937724387343</v>
+        <v>84.81864620060904</v>
       </c>
       <c r="C11" t="n">
-        <v>39.10562843911276</v>
+        <v>41.64394465713973</v>
       </c>
       <c r="D11" t="n">
-        <v>1.721765268086709</v>
+        <v>1.75865694715964</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08411207781397</v>
+        <v>10.75261059057346</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529978718462959</v>
+        <v>0.7473289001002925</v>
       </c>
       <c r="G11" t="n">
-        <v>26.59854082721467</v>
+        <v>28.42745260074602</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63790210492961</v>
+        <v>35.8890981984662</v>
       </c>
       <c r="I11" t="n">
-        <v>3.247822394942828</v>
+        <v>2.572693337936593</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70623669903935</v>
+        <v>4.670805625626826</v>
       </c>
       <c r="K11" t="n">
-        <v>18.25062275612659</v>
+        <v>15.18135379939098</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53563123841677</v>
+        <v>43.08903171590846</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89188243365612</v>
+        <v>99.91433017243916</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.30297754065255</v>
+        <v>82.5908937625633</v>
       </c>
       <c r="C12" t="n">
-        <v>37.16210278548284</v>
+        <v>39.81561511969154</v>
       </c>
       <c r="D12" t="n">
-        <v>1.613923149153152</v>
+        <v>1.664396695364712</v>
       </c>
       <c r="E12" t="n">
-        <v>9.904097713539766</v>
+        <v>10.53392162057502</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538554789567571</v>
+        <v>0.7479761039302696</v>
       </c>
       <c r="G12" t="n">
-        <v>24.93255124285334</v>
+        <v>26.90380192836081</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67735203201082</v>
+        <v>35.92017897401945</v>
       </c>
       <c r="I12" t="n">
-        <v>2.709601180658981</v>
+        <v>2.145767790748857</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711596743479732</v>
+        <v>4.674850649564183</v>
       </c>
       <c r="K12" t="n">
-        <v>20.69702245934745</v>
+        <v>17.40910623743671</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05065746642131</v>
+        <v>42.70381493904019</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90978271125159</v>
+        <v>99.92853629616843</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.7334490667759</v>
+        <v>83.80385286863725</v>
       </c>
       <c r="C13" t="n">
-        <v>35.01123260794014</v>
+        <v>40.81312418597327</v>
       </c>
       <c r="D13" t="n">
-        <v>1.501624976192222</v>
+        <v>1.66573169191481</v>
       </c>
       <c r="E13" t="n">
-        <v>9.591665001503326</v>
+        <v>11.19231657112828</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545956506125512</v>
+        <v>0.7485760483552273</v>
       </c>
       <c r="G13" t="n">
-        <v>23.1977226958458</v>
+        <v>27.23923568818159</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71139992817735</v>
+        <v>36.26284468298064</v>
       </c>
       <c r="I13" t="n">
-        <v>2.260217998116217</v>
+        <v>2.016547883856536</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716222816328445</v>
+        <v>4.678600302220168</v>
       </c>
       <c r="K13" t="n">
-        <v>23.26655093322408</v>
+        <v>16.19614713136274</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64694975937304</v>
+        <v>42.92356429177947</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92473330053726</v>
+        <v>99.93283560911549</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.54222692293254</v>
+        <v>81.68884433694723</v>
       </c>
       <c r="C14" t="n">
-        <v>39.21412108112095</v>
+        <v>39.01092756286995</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5034032235984</v>
+        <v>1.578952173319902</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9370781627763</v>
+        <v>10.88949944162672</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554892543949132</v>
+        <v>0.7490897099756422</v>
       </c>
       <c r="G14" t="n">
-        <v>25.06458840602428</v>
+        <v>25.82015494943647</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59190031212496</v>
+        <v>36.28772770134817</v>
       </c>
       <c r="I14" t="n">
-        <v>2.967959724045492</v>
+        <v>1.681609673892549</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721807839968208</v>
+        <v>4.681810687347761</v>
       </c>
       <c r="K14" t="n">
-        <v>16.45777307706746</v>
+        <v>18.31115566305277</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22929086922132</v>
+        <v>42.62190155508126</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90118502740972</v>
+        <v>99.94398478100399</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.67165232871461</v>
+        <v>80.74294024138247</v>
       </c>
       <c r="C15" t="n">
-        <v>38.80220108091564</v>
+        <v>38.29838101392545</v>
       </c>
       <c r="D15" t="n">
-        <v>1.470879070863653</v>
+        <v>1.539560583496861</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09146328314068</v>
+        <v>10.85587582772129</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756243409173613</v>
+        <v>0.7495314042156983</v>
       </c>
       <c r="G15" t="n">
-        <v>24.52234897966473</v>
+        <v>25.1759955061539</v>
       </c>
       <c r="H15" t="n">
-        <v>36.62842757749844</v>
+        <v>36.30912444475148</v>
       </c>
       <c r="I15" t="n">
-        <v>2.475768701038425</v>
+        <v>1.428281198695132</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726521307335082</v>
+        <v>4.684571276348112</v>
       </c>
       <c r="K15" t="n">
-        <v>17.32834767128537</v>
+        <v>19.25705975861753</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78700792213108</v>
+        <v>42.39697791007762</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91755667433209</v>
+        <v>99.9524186826206</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.17551952075895</v>
+        <v>78.33257291286979</v>
       </c>
       <c r="C16" t="n">
-        <v>36.6886586989201</v>
+        <v>36.10896838178272</v>
       </c>
       <c r="D16" t="n">
-        <v>1.375655238736497</v>
+        <v>1.44152132964517</v>
       </c>
       <c r="E16" t="n">
-        <v>11.65282113923556</v>
+        <v>10.36304631468813</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568926413979811</v>
+        <v>0.7499112249607149</v>
       </c>
       <c r="G16" t="n">
-        <v>22.93478675999697</v>
+        <v>23.57278752534769</v>
       </c>
       <c r="H16" t="n">
-        <v>36.65987294974602</v>
+        <v>36.32752388554868</v>
       </c>
       <c r="I16" t="n">
-        <v>2.064911782908541</v>
+        <v>1.190837476674949</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730579008737382</v>
+        <v>4.686945156004466</v>
       </c>
       <c r="K16" t="n">
-        <v>19.82448047924106</v>
+        <v>21.66742708713021</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41808946903221</v>
+        <v>42.18393005334553</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93122864719336</v>
+        <v>99.96032552225846</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.80053777325941</v>
+        <v>83.64507481242943</v>
       </c>
       <c r="C17" t="n">
-        <v>37.87283964938661</v>
+        <v>39.56544763313267</v>
       </c>
       <c r="D17" t="n">
-        <v>1.376813297017087</v>
+        <v>1.442335748797859</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41161180980641</v>
+        <v>12.20710581050025</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575298110653561</v>
+        <v>0.7503349037865942</v>
       </c>
       <c r="G17" t="n">
-        <v>23.35876696065694</v>
+        <v>25.18802453914105</v>
       </c>
       <c r="H17" t="n">
-        <v>37.09540724424163</v>
+        <v>37.94996696793472</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0658473313135</v>
+        <v>1.417713693602749</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734561319158476</v>
+        <v>4.689593148666211</v>
       </c>
       <c r="K17" t="n">
-        <v>18.19946222674061</v>
+        <v>16.35492518757057</v>
       </c>
       <c r="L17" t="n">
-        <v>43.85889446666649</v>
+        <v>44.03239674005121</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93119634279371</v>
+        <v>99.95276956075445</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.35706591215951</v>
+        <v>85.42443362151451</v>
       </c>
       <c r="C18" t="n">
-        <v>35.74817325790612</v>
+        <v>40.34105010675086</v>
       </c>
       <c r="D18" t="n">
-        <v>1.28717991384967</v>
+        <v>1.443668022187457</v>
       </c>
       <c r="E18" t="n">
-        <v>11.89072117179701</v>
+        <v>12.85252104469005</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580779921038455</v>
+        <v>0.7510279818209112</v>
       </c>
       <c r="G18" t="n">
-        <v>21.83806309046693</v>
+        <v>25.33109574644554</v>
       </c>
       <c r="H18" t="n">
-        <v>37.122251070807</v>
+        <v>37.98502103296062</v>
       </c>
       <c r="I18" t="n">
-        <v>1.722785222486019</v>
+        <v>2.367174907029226</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737987450649035</v>
+        <v>4.693924886380692</v>
       </c>
       <c r="K18" t="n">
-        <v>20.64293408784049</v>
+        <v>14.57556637848548</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55150800616135</v>
+        <v>45.0045505019197</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94261535190796</v>
+        <v>99.92116698715606</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.39387323952296</v>
+        <v>82.73952054750922</v>
       </c>
       <c r="C19" t="n">
-        <v>35.05012522092619</v>
+        <v>38.02217401378161</v>
       </c>
       <c r="D19" t="n">
-        <v>1.252537747167559</v>
+        <v>1.34692394888022</v>
       </c>
       <c r="E19" t="n">
-        <v>11.81012535934498</v>
+        <v>12.32027485910751</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585410396609281</v>
+        <v>0.7516253144606441</v>
       </c>
       <c r="G19" t="n">
-        <v>21.25033031631895</v>
+        <v>23.63359095574334</v>
       </c>
       <c r="H19" t="n">
-        <v>37.14492600379646</v>
+        <v>38.01523254762205</v>
       </c>
       <c r="I19" t="n">
-        <v>1.436531275353279</v>
+        <v>1.974214706316428</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740881497880801</v>
+        <v>4.697658215379023</v>
       </c>
       <c r="K19" t="n">
-        <v>21.60612676047704</v>
+        <v>17.26047945249079</v>
       </c>
       <c r="L19" t="n">
-        <v>43.29589287352771</v>
+        <v>44.651591675199</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95214485493095</v>
+        <v>99.93424514147139</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.86018858187984</v>
+        <v>79.93297875042477</v>
       </c>
       <c r="C20" t="n">
-        <v>32.73736803753725</v>
+        <v>35.52006976809567</v>
       </c>
       <c r="D20" t="n">
-        <v>1.160660402760676</v>
+        <v>1.246435431067424</v>
       </c>
       <c r="E20" t="n">
-        <v>11.14344100858015</v>
+        <v>11.6754939921184</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589402541133231</v>
+        <v>0.752141333041367</v>
       </c>
       <c r="G20" t="n">
-        <v>19.69155580301778</v>
+        <v>21.87038485363867</v>
       </c>
       <c r="H20" t="n">
-        <v>37.16447509938724</v>
+        <v>38.04133141093555</v>
       </c>
       <c r="I20" t="n">
-        <v>1.197739425812409</v>
+        <v>1.646308398114829</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74337658820827</v>
+        <v>4.700883331508541</v>
       </c>
       <c r="K20" t="n">
-        <v>24.13981141812016</v>
+        <v>20.06702124957523</v>
       </c>
       <c r="L20" t="n">
-        <v>43.082916897805</v>
+        <v>44.35806968493143</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9600963534624</v>
+        <v>99.94516070260232</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.76663802503175</v>
+        <v>77.20617450187923</v>
       </c>
       <c r="C21" t="n">
-        <v>36.38962597585353</v>
+        <v>33.04630530550295</v>
       </c>
       <c r="D21" t="n">
-        <v>1.16148360981348</v>
+        <v>1.149428438213655</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11513191215322</v>
+        <v>10.99560857576034</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594785381526138</v>
+        <v>0.7525871057044227</v>
       </c>
       <c r="G21" t="n">
-        <v>21.37934152953767</v>
+        <v>20.16826678612736</v>
       </c>
       <c r="H21" t="n">
-        <v>38.86465362432054</v>
+        <v>38.06387742039453</v>
       </c>
       <c r="I21" t="n">
-        <v>1.739807947600404</v>
+        <v>1.372736765026293</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746740863453837</v>
+        <v>4.703669410652639</v>
       </c>
       <c r="K21" t="n">
-        <v>18.23336197496825</v>
+        <v>22.79382549812075</v>
       </c>
       <c r="L21" t="n">
-        <v>45.31905955416449</v>
+        <v>44.11413840753978</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94204750498626</v>
+        <v>99.95426921116349</v>
       </c>
     </row>
   </sheetData>
